--- a/Tools/Luban/DataTables/Datas/建筑_Building.xlsx
+++ b/Tools/Luban/DataTables/Datas/建筑_Building.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="building" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="building" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Tools/Luban/DataTables/Datas/建筑_Building.xlsx
+++ b/Tools/Luban/DataTables/Datas/建筑_Building.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,8 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +515,16 @@
           <t>level</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>iconSprite</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>worldSprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -570,6 +582,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -625,6 +647,16 @@
       <c r="K3" s="2" t="inlineStr">
         <is>
           <t>等级</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>UI图标sprite</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>世界sprite名</t>
         </is>
       </c>
     </row>
@@ -668,6 +700,12 @@
       <c r="K4" t="n">
         <v>1</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -709,6 +747,12 @@
       <c r="K5" t="n">
         <v>2</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -750,6 +794,16 @@
       <c r="K6" t="n">
         <v>1</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SL_Item_c2_r1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>SL_WorkStation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -791,6 +845,16 @@
       <c r="K7" t="n">
         <v>2</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SL_Item_c3_r1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>SL_WorkStation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -832,6 +896,16 @@
       <c r="K8" t="n">
         <v>1</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SL_Item_c4_r1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>SL_Sign</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -873,6 +947,16 @@
       <c r="K9" t="n">
         <v>1</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SL_Item_c5_r1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>SL_Deco_c6_r3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -914,6 +998,12 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>SL_Item_c6_r1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -955,6 +1045,16 @@
       <c r="K11" t="n">
         <v>1</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SL_Item_c7_r1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SL_Fence_0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -996,6 +1096,16 @@
       <c r="K12" t="n">
         <v>1</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SL_Chest</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1037,6 +1147,12 @@
       <c r="K13" t="n">
         <v>1</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Tools/Luban/DataTables/Datas/建筑_Building.xlsx
+++ b/Tools/Luban/DataTables/Datas/建筑_Building.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,6 +526,11 @@
           <t>worldSprite</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>worldPrefab</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -592,6 +598,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -657,6 +668,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>世界sprite名</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>世界prefab名</t>
         </is>
       </c>
     </row>
@@ -706,6 +722,7 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -753,6 +770,7 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -804,6 +822,7 @@
           <t>SL_WorkStation</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -855,6 +874,7 @@
           <t>SL_WorkStation</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -906,6 +926,7 @@
           <t>SL_Sign</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -957,6 +978,7 @@
           <t>SL_Deco_c6_r3</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1004,6 +1026,7 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1055,6 +1078,7 @@
           <t>SL_Fence_0</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1106,6 +1130,7 @@
           <t>SL_Chest</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1153,6 +1178,7 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
